--- a/verification/model_verification_results_300_buses_raw.xlsx
+++ b/verification/model_verification_results_300_buses_raw.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\bagir\Documents\1) Projects\2) AC verification\verification\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6593666-7983-4C26-8BF9-1241317544A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -178,8 +184,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -196,12 +202,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -231,24 +243,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -286,7 +310,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -320,6 +344,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -354,9 +379,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -529,11 +555,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22.26953125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>24</v>
       </c>
@@ -610,30 +639,30 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B2">
-        <v>2497923</v>
+        <v>556.669677734375</v>
       </c>
       <c r="C2">
-        <v>2269914.5</v>
+        <v>150.17976379394531</v>
       </c>
       <c r="D2">
-        <v>2101301.5</v>
+        <v>0.84534740447998047</v>
       </c>
       <c r="E2">
-        <v>2002367.875</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>2003198</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>1999803</v>
+        <v>1.6367912292480469E-2</v>
       </c>
       <c r="H2">
-        <v>0.01894068717956543</v>
+        <v>4.4768810272216797E-2</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -651,66 +680,66 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>178.7211456298828</v>
+        <v>155.7388610839844</v>
       </c>
       <c r="O2">
-        <v>128.2811126708984</v>
+        <v>105.056510925293</v>
       </c>
       <c r="P2">
-        <v>79.47595977783203</v>
+        <v>55.897140502929688</v>
       </c>
       <c r="Q2">
-        <v>45.3581428527832</v>
+        <v>21.344587326049801</v>
       </c>
       <c r="R2">
-        <v>29.98628807067871</v>
+        <v>5.7999534606933594</v>
       </c>
       <c r="S2">
-        <v>23.93890190124512</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>55.03517913818359</v>
+        <v>32.262161254882813</v>
       </c>
       <c r="U2">
-        <v>43.67824554443359</v>
+        <v>20.046598434448239</v>
       </c>
       <c r="V2">
-        <v>36.29541397094727</v>
+        <v>12.342084884643549</v>
       </c>
       <c r="W2">
-        <v>30.60916519165039</v>
+        <v>6.5396213531494141</v>
       </c>
       <c r="X2">
-        <v>26.0080509185791</v>
+        <v>1.806734085083008</v>
       </c>
       <c r="Y2">
-        <v>23.87102317810059</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B3">
-        <v>2016118.125</v>
+        <v>84.848915100097656</v>
       </c>
       <c r="C3">
-        <v>2009792.375</v>
+        <v>11.30858707427979</v>
       </c>
       <c r="D3">
-        <v>2003414</v>
+        <v>2.5963753461837769E-2</v>
       </c>
       <c r="E3">
-        <v>1999981</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>1997909.625</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>1996173.125</v>
+        <v>2.9228415223769838E-4</v>
       </c>
       <c r="H3">
-        <v>0.0003382265567779541</v>
+        <v>7.9944304889068007E-4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -728,1466 +757,1466 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>27.89418029785156</v>
+        <v>33.609638214111328</v>
       </c>
       <c r="O3">
-        <v>18.45852661132812</v>
+        <v>21.713535308837891</v>
       </c>
       <c r="P3">
-        <v>9.525458335876465</v>
+        <v>10.05096912384033</v>
       </c>
       <c r="Q3">
-        <v>3.879203796386719</v>
+        <v>2.88368821144104</v>
       </c>
       <c r="R3">
-        <v>1.930436849594116</v>
+        <v>0.64118129014968872</v>
       </c>
       <c r="S3">
-        <v>1.199825167655945</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>5.23432445526123</v>
+        <v>4.8401880264282227</v>
       </c>
       <c r="U3">
-        <v>3.656433820724487</v>
+        <v>2.7299962043762211</v>
       </c>
       <c r="V3">
-        <v>2.702985048294067</v>
+        <v>1.581185936927795</v>
       </c>
       <c r="W3">
-        <v>2.013734102249146</v>
+        <v>0.78994476795196533</v>
       </c>
       <c r="X3">
-        <v>1.478559970855713</v>
+        <v>0.1766027361154556</v>
       </c>
       <c r="Y3">
-        <v>1.187878251075745</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B4">
-        <v>2500034.75</v>
+        <v>4932.67822265625</v>
       </c>
       <c r="C4">
-        <v>2271481.75</v>
+        <v>2221.619140625</v>
       </c>
       <c r="D4">
-        <v>2102300</v>
+        <v>631.82122802734375</v>
       </c>
       <c r="E4">
-        <v>2002184.75</v>
+        <v>159.56549072265619</v>
       </c>
       <c r="F4">
-        <v>2002785.625</v>
+        <v>20.710540771484379</v>
       </c>
       <c r="G4">
-        <v>1999402.875</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>30.50162506103516</v>
+        <v>36.247352600097663</v>
       </c>
       <c r="I4">
-        <v>20.82376861572266</v>
+        <v>24.446891784667969</v>
       </c>
       <c r="J4">
-        <v>14.13132095336914</v>
+        <v>16.36537933349609</v>
       </c>
       <c r="K4">
-        <v>9.71527099609375</v>
+        <v>11.054386138916019</v>
       </c>
       <c r="L4">
-        <v>6.646300315856934</v>
+        <v>7.5908832550048828</v>
       </c>
       <c r="M4">
-        <v>4.343445777893066</v>
+        <v>5.0403423309326172</v>
       </c>
       <c r="N4">
-        <v>91.66159057617188</v>
+        <v>92.311874389648438</v>
       </c>
       <c r="O4">
-        <v>62.37477493286133</v>
+        <v>62.893203735351563</v>
       </c>
       <c r="P4">
-        <v>33.12231063842773</v>
+        <v>33.478546142578118</v>
       </c>
       <c r="Q4">
-        <v>11.37866878509521</v>
+        <v>11.517621994018549</v>
       </c>
       <c r="R4">
-        <v>2.012483596801758</v>
+        <v>2.0862350463867192</v>
       </c>
       <c r="S4">
-        <v>0.0380675345659256</v>
+        <v>3.8050472736358643E-2</v>
       </c>
       <c r="T4">
-        <v>16.33071136474609</v>
+        <v>17.2293815612793</v>
       </c>
       <c r="U4">
-        <v>9.04268741607666</v>
+        <v>9.3146076202392578</v>
       </c>
       <c r="V4">
-        <v>4.971866607666016</v>
+        <v>5.0766692161560059</v>
       </c>
       <c r="W4">
-        <v>1.934597969055176</v>
+        <v>2.0124721527099609</v>
       </c>
       <c r="X4">
-        <v>0.3744528293609619</v>
+        <v>0.38329792022705078</v>
       </c>
       <c r="Y4">
-        <v>0.009108006954193115</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25">
+        <v>9.0798884630203247E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B5">
-        <v>2017624.625</v>
+        <v>321.19692993164063</v>
       </c>
       <c r="C5">
-        <v>2010191</v>
+        <v>142.0351257324219</v>
       </c>
       <c r="D5">
-        <v>2004486.375</v>
+        <v>39.859508514404297</v>
       </c>
       <c r="E5">
-        <v>1999497.125</v>
+        <v>9.6434345245361328</v>
       </c>
       <c r="F5">
-        <v>1996950.25</v>
+        <v>1.135125994682312</v>
       </c>
       <c r="G5">
-        <v>1995052.375</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>1.481185793876648</v>
+        <v>1.757803797721863</v>
       </c>
       <c r="I5">
-        <v>0.9933646321296692</v>
+        <v>1.162093043327332</v>
       </c>
       <c r="J5">
-        <v>0.6317781805992126</v>
+        <v>0.74177950620651245</v>
       </c>
       <c r="K5">
-        <v>0.3959234058856964</v>
+        <v>0.45290425419807429</v>
       </c>
       <c r="L5">
-        <v>0.2380574643611908</v>
+        <v>0.27503785490989691</v>
       </c>
       <c r="M5">
-        <v>0.1324248611927032</v>
+        <v>0.15594564378261569</v>
       </c>
       <c r="N5">
-        <v>18.47214317321777</v>
+        <v>22.622976303100589</v>
       </c>
       <c r="O5">
-        <v>12.25269985198975</v>
+        <v>15.035781860351561</v>
       </c>
       <c r="P5">
-        <v>5.507229804992676</v>
+        <v>6.8163657188415527</v>
       </c>
       <c r="Q5">
-        <v>0.9745446443557739</v>
+        <v>1.207345724105835</v>
       </c>
       <c r="R5">
-        <v>0.1610523015260696</v>
+        <v>0.2001827955245972</v>
       </c>
       <c r="S5">
-        <v>0.001044595614075661</v>
+        <v>1.2679488863796E-3</v>
       </c>
       <c r="T5">
-        <v>1.660136461257935</v>
+        <v>2.179246187210083</v>
       </c>
       <c r="U5">
-        <v>0.7581215500831604</v>
+        <v>0.96092325448989868</v>
       </c>
       <c r="V5">
-        <v>0.3358121514320374</v>
+        <v>0.41963419318199158</v>
       </c>
       <c r="W5">
-        <v>0.1576278358697891</v>
+        <v>0.19613189995288849</v>
       </c>
       <c r="X5">
-        <v>0.03980468213558197</v>
+        <v>4.9279015511274338E-2</v>
       </c>
       <c r="Y5">
-        <v>0.0002182376338168979</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25">
-      <c r="A6" s="1" t="s">
+        <v>2.6697511202655733E-4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B6">
-        <v>2500034.75</v>
-      </c>
-      <c r="C6">
-        <v>2271481.75</v>
-      </c>
-      <c r="D6">
-        <v>2102300</v>
-      </c>
-      <c r="E6">
-        <v>2002367.875</v>
-      </c>
-      <c r="F6">
-        <v>2003198</v>
-      </c>
-      <c r="G6">
-        <v>1999803</v>
-      </c>
-      <c r="H6">
-        <v>30.50162506103516</v>
-      </c>
-      <c r="I6">
-        <v>20.82376861572266</v>
-      </c>
-      <c r="J6">
-        <v>14.13132095336914</v>
-      </c>
-      <c r="K6">
-        <v>9.71527099609375</v>
-      </c>
-      <c r="L6">
-        <v>6.646300315856934</v>
-      </c>
-      <c r="M6">
-        <v>4.343445777893066</v>
-      </c>
-      <c r="N6">
-        <v>178.7211456298828</v>
-      </c>
-      <c r="O6">
-        <v>128.2811126708984</v>
-      </c>
-      <c r="P6">
-        <v>79.47595977783203</v>
-      </c>
-      <c r="Q6">
-        <v>45.3581428527832</v>
-      </c>
-      <c r="R6">
-        <v>29.98628807067871</v>
-      </c>
-      <c r="S6">
-        <v>23.93890190124512</v>
-      </c>
-      <c r="T6">
-        <v>55.03517913818359</v>
-      </c>
-      <c r="U6">
-        <v>43.67824554443359</v>
-      </c>
-      <c r="V6">
-        <v>36.29541397094727</v>
-      </c>
-      <c r="W6">
-        <v>30.60916519165039</v>
-      </c>
-      <c r="X6">
-        <v>26.0080509185791</v>
-      </c>
-      <c r="Y6">
-        <v>23.87102317810059</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25">
+      <c r="B6" s="3">
+        <v>4932.67822265625</v>
+      </c>
+      <c r="C6" s="3">
+        <v>2221.619140625</v>
+      </c>
+      <c r="D6" s="3">
+        <v>631.82122802734375</v>
+      </c>
+      <c r="E6" s="3">
+        <v>159.56549072265619</v>
+      </c>
+      <c r="F6" s="3">
+        <v>20.710540771484379</v>
+      </c>
+      <c r="G6" s="3">
+        <v>1.6367912292480469E-2</v>
+      </c>
+      <c r="H6" s="3">
+        <v>36.247352600097663</v>
+      </c>
+      <c r="I6" s="3">
+        <v>24.446891784667969</v>
+      </c>
+      <c r="J6" s="3">
+        <v>16.36537933349609</v>
+      </c>
+      <c r="K6" s="3">
+        <v>11.054386138916019</v>
+      </c>
+      <c r="L6" s="3">
+        <v>7.5908832550048828</v>
+      </c>
+      <c r="M6" s="3">
+        <v>5.0403423309326172</v>
+      </c>
+      <c r="N6" s="3">
+        <v>155.7388610839844</v>
+      </c>
+      <c r="O6" s="3">
+        <v>105.056510925293</v>
+      </c>
+      <c r="P6" s="3">
+        <v>55.897140502929688</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>21.344587326049801</v>
+      </c>
+      <c r="R6" s="3">
+        <v>5.7999534606933594</v>
+      </c>
+      <c r="S6" s="3">
+        <v>3.8050472736358643E-2</v>
+      </c>
+      <c r="T6" s="3">
+        <v>32.262161254882813</v>
+      </c>
+      <c r="U6" s="3">
+        <v>20.046598434448239</v>
+      </c>
+      <c r="V6" s="3">
+        <v>12.342084884643549</v>
+      </c>
+      <c r="W6" s="3">
+        <v>6.5396213531494141</v>
+      </c>
+      <c r="X6" s="3">
+        <v>1.806734085083008</v>
+      </c>
+      <c r="Y6" s="3">
+        <v>9.0798884630203247E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B7">
-        <v>2016871.625</v>
+        <v>203.0229187011719</v>
       </c>
       <c r="C7">
-        <v>2009991.75</v>
+        <v>76.671859741210938</v>
       </c>
       <c r="D7">
-        <v>2003950.25</v>
+        <v>19.9427375793457</v>
       </c>
       <c r="E7">
-        <v>1999739.125</v>
+        <v>4.8217172622680664</v>
       </c>
       <c r="F7">
-        <v>1997430</v>
+        <v>0.56756299734115601</v>
       </c>
       <c r="G7">
-        <v>1995612.75</v>
+        <v>1.4614207611884919E-4</v>
       </c>
       <c r="H7">
-        <v>0.740761935710907</v>
+        <v>0.87930160760879517</v>
       </c>
       <c r="I7">
-        <v>0.4966823160648346</v>
+        <v>0.58104658126831055</v>
       </c>
       <c r="J7">
-        <v>0.3158890902996063</v>
+        <v>0.37088975310325623</v>
       </c>
       <c r="K7">
-        <v>0.1979617029428482</v>
+        <v>0.2264521270990372</v>
       </c>
       <c r="L7">
-        <v>0.1190287321805954</v>
+        <v>0.1375189274549484</v>
       </c>
       <c r="M7">
-        <v>0.06621243059635162</v>
+        <v>7.7972821891307831E-2</v>
       </c>
       <c r="N7">
-        <v>27.72888374328613</v>
+        <v>28.116306304931641</v>
       </c>
       <c r="O7">
-        <v>18.34965133666992</v>
+        <v>18.37465858459473</v>
       </c>
       <c r="P7">
-        <v>9.454964637756348</v>
+        <v>8.4336681365966797</v>
       </c>
       <c r="Q7">
-        <v>3.828244924545288</v>
+        <v>2.0455169677734379</v>
       </c>
       <c r="R7">
-        <v>1.899394989013672</v>
+        <v>0.42068201303482061</v>
       </c>
       <c r="S7">
-        <v>1.178793787956238</v>
+        <v>6.3397444318979979E-4</v>
       </c>
       <c r="T7">
-        <v>5.171619415283203</v>
+        <v>3.5097172260284419</v>
       </c>
       <c r="U7">
-        <v>3.605586051940918</v>
+        <v>1.8454598188400271</v>
       </c>
       <c r="V7">
-        <v>2.661455631256104</v>
+        <v>1.0004099607467649</v>
       </c>
       <c r="W7">
-        <v>1.981170892715454</v>
+        <v>0.4930383563041687</v>
       </c>
       <c r="X7">
-        <v>1.45331859588623</v>
+        <v>0.11294087022542949</v>
       </c>
       <c r="Y7">
-        <v>1.167042016983032</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25">
+        <v>1.3348755601327869E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B8">
-        <v>1469072.625</v>
+        <v>3728.604736328125</v>
       </c>
       <c r="C8">
-        <v>834295.5</v>
+        <v>1517.879516601562</v>
       </c>
       <c r="D8">
-        <v>291475.46875</v>
+        <v>400.39480590820313</v>
       </c>
       <c r="E8">
-        <v>77979.5546875</v>
+        <v>100.39051818847661</v>
       </c>
       <c r="F8">
-        <v>15558.8515625</v>
+        <v>10.877223014831539</v>
       </c>
       <c r="G8">
-        <v>2873.963623046875</v>
+        <v>2.2963213920593262</v>
       </c>
       <c r="H8">
-        <v>27.25114440917969</v>
+        <v>34.558731079101563</v>
       </c>
       <c r="I8">
-        <v>14.4057788848877</v>
+        <v>19.984233856201168</v>
       </c>
       <c r="J8">
-        <v>5.389522552490234</v>
+        <v>8.6401290893554688</v>
       </c>
       <c r="K8">
-        <v>3.322885513305664</v>
+        <v>4.0213222503662109</v>
       </c>
       <c r="L8">
-        <v>1.796999216079712</v>
+        <v>2.2729167938232422</v>
       </c>
       <c r="M8">
-        <v>1.519181489944458</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25">
+        <v>1.551225900650024</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B9">
-        <v>84838.2109375</v>
+        <v>250.65437316894531</v>
       </c>
       <c r="C9">
-        <v>47537.6796875</v>
+        <v>98.761344909667969</v>
       </c>
       <c r="D9">
-        <v>17328.703125</v>
+        <v>24.352895736694339</v>
       </c>
       <c r="E9">
-        <v>5646.10693359375</v>
+        <v>5.7630419731140137</v>
       </c>
       <c r="F9">
-        <v>1465.528442382812</v>
+        <v>0.84886157512664795</v>
       </c>
       <c r="G9">
-        <v>407.5045776367188</v>
+        <v>0.14886376261711121</v>
       </c>
       <c r="H9">
-        <v>2.082605123519897</v>
+        <v>2.389291524887085</v>
       </c>
       <c r="I9">
-        <v>1.222244501113892</v>
+        <v>1.380934596061707</v>
       </c>
       <c r="J9">
-        <v>0.6175691485404968</v>
+        <v>0.72217357158660889</v>
       </c>
       <c r="K9">
-        <v>0.3173990845680237</v>
+        <v>0.34903660416603088</v>
       </c>
       <c r="L9">
-        <v>0.1856433004140854</v>
+        <v>0.18616798520088201</v>
       </c>
       <c r="M9">
-        <v>0.09197846800088882</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25">
+        <v>9.0956531465053558E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B10">
-        <v>1466614.25</v>
+        <v>1480.799072265625</v>
       </c>
       <c r="C10">
-        <v>832147.6875</v>
+        <v>126.151611328125</v>
       </c>
       <c r="D10">
-        <v>289555.03125</v>
+        <v>18.8858757019043</v>
       </c>
       <c r="E10">
-        <v>79935.5078125</v>
+        <v>31.651313781738281</v>
       </c>
       <c r="F10">
-        <v>17554.02734375</v>
+        <v>11.123519897460939</v>
       </c>
       <c r="G10">
-        <v>1550.1796875</v>
+        <v>2.9962177276611328</v>
       </c>
       <c r="H10">
-        <v>17.69809341430664</v>
+        <v>17.293203353881839</v>
       </c>
       <c r="I10">
-        <v>4.529706001281738</v>
+        <v>4.5568537712097168</v>
       </c>
       <c r="J10">
-        <v>3.263203144073486</v>
+        <v>3.099699735641479</v>
       </c>
       <c r="K10">
-        <v>2.930870056152344</v>
+        <v>2.7645092010498051</v>
       </c>
       <c r="L10">
-        <v>2.635218858718872</v>
+        <v>2.4559264183044429</v>
       </c>
       <c r="M10">
-        <v>2.359278440475464</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25">
+        <v>2.1636137962341309</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B11">
-        <v>83290.125</v>
+        <v>123.6346054077148</v>
       </c>
       <c r="C11">
-        <v>46386.4296875</v>
+        <v>21.726324081420898</v>
       </c>
       <c r="D11">
-        <v>16721.060546875</v>
+        <v>2.0358197689056401</v>
       </c>
       <c r="E11">
-        <v>5523.171875</v>
+        <v>1.7170771360397341</v>
       </c>
       <c r="F11">
-        <v>1359.125610351562</v>
+        <v>0.56055325269699097</v>
       </c>
       <c r="G11">
-        <v>340.4155883789062</v>
+        <v>0.146727129817009</v>
       </c>
       <c r="H11">
-        <v>0.9621809720993042</v>
+        <v>1.003059029579163</v>
       </c>
       <c r="I11">
-        <v>0.3315540254116058</v>
+        <v>0.25105521082878107</v>
       </c>
       <c r="J11">
-        <v>0.1305826455354691</v>
+        <v>0.12059769779443739</v>
       </c>
       <c r="K11">
-        <v>0.07126997411251068</v>
+        <v>6.5455310046672821E-2</v>
       </c>
       <c r="L11">
-        <v>0.05488209053874016</v>
+        <v>5.0950285047292709E-2</v>
       </c>
       <c r="M11">
-        <v>0.04832605645060539</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25">
-      <c r="A12" s="1" t="s">
+        <v>4.4260509312152863E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B12">
-        <v>1469072.625</v>
-      </c>
-      <c r="C12">
-        <v>834295.5</v>
-      </c>
-      <c r="D12">
-        <v>291475.46875</v>
-      </c>
-      <c r="E12">
-        <v>79935.5078125</v>
-      </c>
-      <c r="F12">
-        <v>17554.02734375</v>
-      </c>
-      <c r="G12">
-        <v>2873.963623046875</v>
-      </c>
-      <c r="H12">
-        <v>27.25114440917969</v>
-      </c>
-      <c r="I12">
-        <v>14.4057788848877</v>
-      </c>
-      <c r="J12">
-        <v>5.389522552490234</v>
-      </c>
-      <c r="K12">
-        <v>3.322885513305664</v>
-      </c>
-      <c r="L12">
-        <v>2.635218858718872</v>
-      </c>
-      <c r="M12">
-        <v>2.359278440475464</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25">
+      <c r="B12" s="3">
+        <v>3728.604736328125</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1517.879516601562</v>
+      </c>
+      <c r="D12" s="3">
+        <v>400.39480590820313</v>
+      </c>
+      <c r="E12" s="3">
+        <v>100.39051818847661</v>
+      </c>
+      <c r="F12" s="3">
+        <v>11.123519897460939</v>
+      </c>
+      <c r="G12" s="3">
+        <v>2.9962177276611328</v>
+      </c>
+      <c r="H12" s="3">
+        <v>34.558731079101563</v>
+      </c>
+      <c r="I12" s="3">
+        <v>19.984233856201168</v>
+      </c>
+      <c r="J12" s="3">
+        <v>8.6401290893554688</v>
+      </c>
+      <c r="K12" s="3">
+        <v>4.0213222503662109</v>
+      </c>
+      <c r="L12" s="3">
+        <v>2.4559264183044429</v>
+      </c>
+      <c r="M12" s="3">
+        <v>2.1636137962341309</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B13">
-        <v>84064.171875</v>
+        <v>187.14451599121091</v>
       </c>
       <c r="C13">
-        <v>46962.0546875</v>
+        <v>60.24383544921875</v>
       </c>
       <c r="D13">
-        <v>17024.880859375</v>
+        <v>13.194357872009279</v>
       </c>
       <c r="E13">
-        <v>5584.6396484375</v>
+        <v>3.740059375762939</v>
       </c>
       <c r="F13">
-        <v>1412.326904296875</v>
+        <v>0.70470744371414185</v>
       </c>
       <c r="G13">
-        <v>373.9601440429688</v>
+        <v>0.14779543876647949</v>
       </c>
       <c r="H13">
-        <v>1.522393107414246</v>
+        <v>1.696175217628479</v>
       </c>
       <c r="I13">
-        <v>0.7768992781639099</v>
+        <v>0.81599491834640503</v>
       </c>
       <c r="J13">
-        <v>0.3740759193897247</v>
+        <v>0.42138567566871638</v>
       </c>
       <c r="K13">
-        <v>0.1943345218896866</v>
+        <v>0.20724594593048101</v>
       </c>
       <c r="L13">
-        <v>0.1202626973390579</v>
+        <v>0.1185591369867325</v>
       </c>
       <c r="M13">
-        <v>0.07015226036310196</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25">
-      <c r="A14" s="1" t="s">
+        <v>6.760852038860321E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B14">
-        <v>5692.4697265625</v>
-      </c>
-      <c r="C14">
-        <v>3078.30419921875</v>
-      </c>
-      <c r="D14">
-        <v>936.630615234375</v>
-      </c>
-      <c r="E14">
-        <v>236.65087890625</v>
-      </c>
-      <c r="F14">
-        <v>0.7152934074401855</v>
-      </c>
-      <c r="G14">
-        <v>0.1233410835266113</v>
-      </c>
-      <c r="H14">
-        <v>1.437595844268799</v>
-      </c>
-      <c r="I14">
-        <v>1.180083751678467</v>
-      </c>
-      <c r="J14">
-        <v>0.9623870849609375</v>
-      </c>
-      <c r="K14">
-        <v>0.7668304443359375</v>
-      </c>
-      <c r="L14">
-        <v>0.5952425003051758</v>
-      </c>
-      <c r="M14">
-        <v>0.4799623489379883</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25">
+      <c r="B14" s="3">
+        <v>5737.74755859375</v>
+      </c>
+      <c r="C14" s="3">
+        <v>3113.263916015625</v>
+      </c>
+      <c r="D14" s="3">
+        <v>951.8182373046875</v>
+      </c>
+      <c r="E14" s="3">
+        <v>239.1918029785156</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.71743917465209961</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0.12584257125854489</v>
+      </c>
+      <c r="H14" s="3">
+        <v>1.5265259742736821</v>
+      </c>
+      <c r="I14" s="3">
+        <v>1.2279982566833501</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0.99684762954711914</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0.79260349273681641</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0.61135292053222656</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0.48315858840942377</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B15">
-        <v>140.7614440917969</v>
+        <v>142.6114807128906</v>
       </c>
       <c r="C15">
-        <v>72.32025146484375</v>
+        <v>73.555442810058594</v>
       </c>
       <c r="D15">
-        <v>18.72768783569336</v>
+        <v>19.27617263793945</v>
       </c>
       <c r="E15">
-        <v>1.791234254837036</v>
+        <v>1.8100878000259399</v>
       </c>
       <c r="F15">
-        <v>0.005989273078739643</v>
+        <v>6.0295285657048234E-3</v>
       </c>
       <c r="G15">
-        <v>0.0005630147643387318</v>
+        <v>6.0364569071680307E-4</v>
       </c>
       <c r="H15">
-        <v>0.02391748875379562</v>
+        <v>2.7572464197874069E-2</v>
       </c>
       <c r="I15">
-        <v>0.01206401363015175</v>
+        <v>1.3802036643028259E-2</v>
       </c>
       <c r="J15">
-        <v>0.006682929582893848</v>
+        <v>7.1854670532047749E-3</v>
       </c>
       <c r="K15">
-        <v>0.004120433237403631</v>
+        <v>4.2671617120504379E-3</v>
       </c>
       <c r="L15">
-        <v>0.002687758533284068</v>
+        <v>2.7515443507581949E-3</v>
       </c>
       <c r="M15">
-        <v>0.002154590329155326</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25">
+        <v>2.167046302929521E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B16">
-        <v>3.357231616973877</v>
+        <v>3.399739265441895</v>
       </c>
       <c r="C16">
-        <v>1.790279388427734</v>
+        <v>1.8035209178924561</v>
       </c>
       <c r="D16">
-        <v>1.040657043457031</v>
+        <v>1.0452935695648189</v>
       </c>
       <c r="E16">
-        <v>0.3892583847045898</v>
+        <v>0.39153289794921881</v>
       </c>
       <c r="F16">
-        <v>0.1251627206802368</v>
+        <v>0.1256893873214722</v>
       </c>
       <c r="G16">
-        <v>0.06193161010742188</v>
+        <v>6.1914920806884773E-2</v>
       </c>
       <c r="H16">
-        <v>0.3595700263977051</v>
+        <v>0.38149666786193848</v>
       </c>
       <c r="I16">
-        <v>0.2776938676834106</v>
+        <v>0.29309797286987299</v>
       </c>
       <c r="J16">
-        <v>0.1998186111450195</v>
+        <v>0.2105132341384888</v>
       </c>
       <c r="K16">
-        <v>0.1538453102111816</v>
+        <v>0.15854430198669431</v>
       </c>
       <c r="L16">
-        <v>0.110068678855896</v>
+        <v>0.1127555370330811</v>
       </c>
       <c r="M16">
-        <v>0.07021236419677734</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25">
+        <v>7.0709228515625E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B17">
-        <v>1.448837637901306</v>
+        <v>1.4678653478622441</v>
       </c>
       <c r="C17">
-        <v>0.8112905025482178</v>
+        <v>0.82029324769973755</v>
       </c>
       <c r="D17">
-        <v>0.3885625898838043</v>
+        <v>0.39523455500602722</v>
       </c>
       <c r="E17">
-        <v>0.1224560290575027</v>
+        <v>0.12343673408031459</v>
       </c>
       <c r="F17">
-        <v>0.0320555604994297</v>
+        <v>3.2289471477270133E-2</v>
       </c>
       <c r="G17">
-        <v>0.008209339343011379</v>
+        <v>8.2240328192710876E-3</v>
       </c>
       <c r="H17">
-        <v>0.1036851704120636</v>
+        <v>0.1117731109261513</v>
       </c>
       <c r="I17">
-        <v>0.07580725103616714</v>
+        <v>8.0999195575714111E-2</v>
       </c>
       <c r="J17">
-        <v>0.05180945992469788</v>
+        <v>5.498431995511055E-2</v>
       </c>
       <c r="K17">
-        <v>0.03299428150057793</v>
+        <v>3.4585569053888321E-2</v>
       </c>
       <c r="L17">
-        <v>0.01788991689682007</v>
+        <v>1.854072883725166E-2</v>
       </c>
       <c r="M17">
-        <v>0.008068781346082687</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25">
+        <v>8.0782314762473106E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B18">
-        <v>3.357231616973877</v>
+        <v>3.399739265441895</v>
       </c>
       <c r="C18">
-        <v>1.790279388427734</v>
+        <v>1.8035209178924561</v>
       </c>
       <c r="D18">
-        <v>1.040657043457031</v>
+        <v>1.0452935695648189</v>
       </c>
       <c r="E18">
-        <v>0.3892583847045898</v>
+        <v>0.39153289794921881</v>
       </c>
       <c r="F18">
-        <v>0.1251627206802368</v>
+        <v>0.1256893873214722</v>
       </c>
       <c r="G18">
-        <v>0.06193161010742188</v>
+        <v>6.1914920806884773E-2</v>
       </c>
       <c r="H18">
-        <v>0.3595700263977051</v>
+        <v>0.38149666786193848</v>
       </c>
       <c r="I18">
-        <v>0.2776938676834106</v>
+        <v>0.29309797286987299</v>
       </c>
       <c r="J18">
-        <v>0.1998186111450195</v>
+        <v>0.2105132341384888</v>
       </c>
       <c r="K18">
-        <v>0.1538453102111816</v>
+        <v>0.15854430198669431</v>
       </c>
       <c r="L18">
-        <v>0.110068678855896</v>
+        <v>0.1127555370330811</v>
       </c>
       <c r="M18">
-        <v>0.07021236419677734</v>
+        <v>7.0709228515625E-2</v>
       </c>
       <c r="N18">
-        <v>1.354787349700928</v>
+        <v>1.3656270503997801</v>
       </c>
       <c r="O18">
-        <v>0.9157299995422363</v>
+        <v>0.9245455265045166</v>
       </c>
       <c r="P18">
-        <v>0.4860937595367432</v>
+        <v>0.49256682395935059</v>
       </c>
       <c r="Q18">
-        <v>0.1639794111251831</v>
+        <v>0.1665990352630615</v>
       </c>
       <c r="R18">
-        <v>0.03734874725341797</v>
+        <v>3.8019180297851563E-2</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
       <c r="T18">
-        <v>0.2017276287078857</v>
+        <v>0.2127885818481445</v>
       </c>
       <c r="U18">
-        <v>0.1242213249206543</v>
+        <v>0.12835693359375</v>
       </c>
       <c r="V18">
-        <v>0.07558679580688477</v>
+        <v>7.7667117118835449E-2</v>
       </c>
       <c r="W18">
-        <v>0.03885471820831299</v>
+        <v>4.0062427520751953E-2</v>
       </c>
       <c r="X18">
-        <v>0.008562445640563965</v>
+        <v>9.5038414001464844E-3</v>
       </c>
       <c r="Y18">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B19">
-        <v>1.831585168838501</v>
+        <v>1.854066014289856</v>
       </c>
       <c r="C19">
-        <v>1.028561472892761</v>
+        <v>1.0400325059890749</v>
       </c>
       <c r="D19">
-        <v>0.5237080454826355</v>
+        <v>0.53205758333206177</v>
       </c>
       <c r="E19">
-        <v>0.1759632676839828</v>
+        <v>0.1770375669002533</v>
       </c>
       <c r="F19">
-        <v>0.05621723458170891</v>
+        <v>5.6573953479528427E-2</v>
       </c>
       <c r="G19">
-        <v>0.01786315627396107</v>
+        <v>1.7896603792905811E-2</v>
       </c>
       <c r="H19">
-        <v>0.1477359980344772</v>
+        <v>0.1568730175495148</v>
       </c>
       <c r="I19">
-        <v>0.1152418702840805</v>
+        <v>0.12137596309185029</v>
       </c>
       <c r="J19">
-        <v>0.08496870845556259</v>
+        <v>8.9177496731281281E-2</v>
       </c>
       <c r="K19">
-        <v>0.0574544332921505</v>
+        <v>5.9811506420373917E-2</v>
       </c>
       <c r="L19">
-        <v>0.03483148291707039</v>
+        <v>3.5800088196992867E-2</v>
       </c>
       <c r="M19">
-        <v>0.01756813749670982</v>
+        <v>1.7562564462423321E-2</v>
       </c>
       <c r="N19">
-        <v>0.80889892578125</v>
+        <v>0.81882369518280029</v>
       </c>
       <c r="O19">
-        <v>0.534179151058197</v>
+        <v>0.54232966899871826</v>
       </c>
       <c r="P19">
-        <v>0.2674725651741028</v>
+        <v>0.27321663498878479</v>
       </c>
       <c r="Q19">
-        <v>0.08102182298898697</v>
+        <v>8.4108144044876099E-2</v>
       </c>
       <c r="R19">
-        <v>0.01500730682164431</v>
+        <v>1.5989791601896289E-2</v>
       </c>
       <c r="S19">
         <v>0</v>
       </c>
       <c r="T19">
-        <v>0.1211694702506065</v>
+        <v>0.1315414160490036</v>
       </c>
       <c r="U19">
-        <v>0.06778056174516678</v>
+        <v>7.2959952056407928E-2</v>
       </c>
       <c r="V19">
-        <v>0.03635141626000404</v>
+        <v>3.9291039109230042E-2</v>
       </c>
       <c r="W19">
-        <v>0.0148938000202179</v>
+        <v>1.6493607312440869E-2</v>
       </c>
       <c r="X19">
-        <v>0.002235169988125563</v>
+        <v>2.5617550127208229E-3</v>
       </c>
       <c r="Y19">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B20">
-        <v>2.393733978271484</v>
+        <v>2.409298181533813</v>
       </c>
       <c r="C20">
-        <v>1.541602849960327</v>
+        <v>1.5557024478912349</v>
       </c>
       <c r="D20">
-        <v>0.9108054041862488</v>
+        <v>0.91490858793258667</v>
       </c>
       <c r="E20">
-        <v>0.7133550047874451</v>
+        <v>0.71643847227096558</v>
       </c>
       <c r="F20">
-        <v>0.4242442846298218</v>
+        <v>0.42594873905181879</v>
       </c>
       <c r="G20">
-        <v>0.03713053464889526</v>
+        <v>3.7236928939819343E-2</v>
       </c>
       <c r="H20">
-        <v>0.6352155208587646</v>
+        <v>0.65843367576599121</v>
       </c>
       <c r="I20">
-        <v>0.5463789701461792</v>
+        <v>0.56481480598449707</v>
       </c>
       <c r="J20">
-        <v>0.4578336477279663</v>
+        <v>0.47167694568634028</v>
       </c>
       <c r="K20">
-        <v>0.3235751986503601</v>
+        <v>0.33204859495162958</v>
       </c>
       <c r="L20">
-        <v>0.1315180659294128</v>
+        <v>0.13543063402175901</v>
       </c>
       <c r="M20">
-        <v>0.0677189826965332</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25">
+        <v>6.5714716911315918E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B21">
-        <v>1.164409637451172</v>
+        <v>1.176805377006531</v>
       </c>
       <c r="C21">
-        <v>0.7801796197891235</v>
+        <v>0.78668671846389771</v>
       </c>
       <c r="D21">
-        <v>0.5058056116104126</v>
+        <v>0.50912779569625854</v>
       </c>
       <c r="E21">
-        <v>0.2954097092151642</v>
+        <v>0.29697754979133612</v>
       </c>
       <c r="F21">
-        <v>0.01904180459678173</v>
+        <v>1.913136430084705E-2</v>
       </c>
       <c r="G21">
-        <v>0.0006614474696107209</v>
+        <v>6.6095608053728938E-4</v>
       </c>
       <c r="H21">
-        <v>0.2281298041343689</v>
+        <v>0.25627988576889038</v>
       </c>
       <c r="I21">
-        <v>0.1555755734443665</v>
+        <v>0.17216974496841431</v>
       </c>
       <c r="J21">
-        <v>0.0747687816619873</v>
+        <v>8.4215223789215088E-2</v>
       </c>
       <c r="K21">
-        <v>0.02274291031062603</v>
+        <v>2.4519894272089001E-2</v>
       </c>
       <c r="L21">
-        <v>0.007464018650352955</v>
+        <v>7.715980987995863E-3</v>
       </c>
       <c r="M21">
-        <v>0.003237003926187754</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25">
+        <v>3.2127241138368841E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B22">
-        <v>2.393733978271484</v>
+        <v>2.409298181533813</v>
       </c>
       <c r="C22">
-        <v>1.541602849960327</v>
+        <v>1.5557024478912349</v>
       </c>
       <c r="D22">
-        <v>0.9108054041862488</v>
+        <v>0.91490858793258667</v>
       </c>
       <c r="E22">
-        <v>0.7133550047874451</v>
+        <v>0.71643847227096558</v>
       </c>
       <c r="F22">
-        <v>0.3939589858055115</v>
+        <v>0.39523285627365112</v>
       </c>
       <c r="G22">
-        <v>0.003643929958343506</v>
+        <v>3.7851929664611821E-3</v>
       </c>
       <c r="H22">
-        <v>0.5998647809028625</v>
+        <v>0.62427133321762085</v>
       </c>
       <c r="I22">
-        <v>0.505206286907196</v>
+        <v>0.52416008710861206</v>
       </c>
       <c r="J22">
-        <v>0.4120339751243591</v>
+        <v>0.42571562528610229</v>
       </c>
       <c r="K22">
-        <v>0.3235751986503601</v>
+        <v>0.33204859495162958</v>
       </c>
       <c r="L22">
-        <v>0.1315180659294128</v>
+        <v>0.13543063402175901</v>
       </c>
       <c r="M22">
-        <v>0.0677189826965332</v>
+        <v>6.5714716911315918E-2</v>
       </c>
       <c r="N22">
-        <v>0.4713399708271027</v>
+        <v>0.47642773389816279</v>
       </c>
       <c r="O22">
-        <v>0.3106951713562012</v>
+        <v>0.31479746103286738</v>
       </c>
       <c r="P22">
-        <v>0.1483206152915955</v>
+        <v>0.15053254365921021</v>
       </c>
       <c r="Q22">
-        <v>0.04170417785644531</v>
+        <v>4.2337000370025628E-2</v>
       </c>
       <c r="R22">
-        <v>0.009359002113342285</v>
+        <v>9.5703601837158203E-3</v>
       </c>
       <c r="S22">
         <v>0</v>
       </c>
       <c r="T22">
-        <v>0.05552160739898682</v>
+        <v>6.0268402099609382E-2</v>
       </c>
       <c r="U22">
-        <v>0.01978063583374023</v>
+        <v>2.1529436111450199E-2</v>
       </c>
       <c r="V22">
-        <v>0.01107710599899292</v>
+        <v>1.111751794815063E-2</v>
       </c>
       <c r="W22">
-        <v>0.00587761402130127</v>
+        <v>5.8922171592712402E-3</v>
       </c>
       <c r="X22">
-        <v>0.00127112865447998</v>
+        <v>1.34509801864624E-3</v>
       </c>
       <c r="Y22">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B23">
-        <v>1.297709584236145</v>
+        <v>1.312357902526855</v>
       </c>
       <c r="C23">
-        <v>0.8549327254295349</v>
+        <v>0.86212968826293945</v>
       </c>
       <c r="D23">
-        <v>0.5353649258613586</v>
+        <v>0.53898447751998901</v>
       </c>
       <c r="E23">
-        <v>0.3393459916114807</v>
+        <v>0.34096270799636841</v>
       </c>
       <c r="F23">
-        <v>0.02955235727131367</v>
+        <v>2.9693696647882462E-2</v>
       </c>
       <c r="G23">
-        <v>6.507017678814009E-05</v>
+        <v>6.759272946510464E-5</v>
       </c>
       <c r="H23">
-        <v>0.2489852905273438</v>
+        <v>0.26606974005699158</v>
       </c>
       <c r="I23">
-        <v>0.1823447048664093</v>
+        <v>0.18904270231723791</v>
       </c>
       <c r="J23">
-        <v>0.0920431986451149</v>
+        <v>9.5656000077724457E-2</v>
       </c>
       <c r="K23">
-        <v>0.03888734430074692</v>
+        <v>4.0468044579029083E-2</v>
       </c>
       <c r="L23">
-        <v>0.01477750670164824</v>
+        <v>1.5264260582625869E-2</v>
       </c>
       <c r="M23">
-        <v>0.005557410418987274</v>
+        <v>5.4760673083364964E-3</v>
       </c>
       <c r="N23">
-        <v>0.3121487498283386</v>
+        <v>0.31048300862312322</v>
       </c>
       <c r="O23">
-        <v>0.2021393477916718</v>
+        <v>0.20159503817558291</v>
       </c>
       <c r="P23">
-        <v>0.07651751488447189</v>
+        <v>7.6654374599456787E-2</v>
       </c>
       <c r="Q23">
-        <v>0.00216631917282939</v>
+        <v>2.3395691532641649E-3</v>
       </c>
       <c r="R23">
-        <v>0.0001671250356594101</v>
+        <v>1.9536211038939649E-4</v>
       </c>
       <c r="S23">
         <v>0</v>
       </c>
       <c r="T23">
-        <v>0.006607718765735626</v>
+        <v>7.1053477004170418E-3</v>
       </c>
       <c r="U23">
-        <v>0.001505618682131171</v>
+        <v>1.533573144115508E-3</v>
       </c>
       <c r="V23">
-        <v>0.0001978054642677307</v>
+        <v>2.6929029263555998E-4</v>
       </c>
       <c r="W23">
-        <v>0.0001049573911586776</v>
+        <v>1.201875056722201E-4</v>
       </c>
       <c r="X23">
-        <v>2.269872675242368E-05</v>
+        <v>1.9780853108386509E-5</v>
       </c>
       <c r="Y23">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:25">
-      <c r="A24" s="1" t="s">
+    <row r="24" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B24">
-        <v>3.357231616973877</v>
-      </c>
-      <c r="C24">
-        <v>1.790279388427734</v>
-      </c>
-      <c r="D24">
-        <v>1.040657043457031</v>
-      </c>
-      <c r="E24">
-        <v>0.7133550047874451</v>
-      </c>
-      <c r="F24">
-        <v>0.4242442846298218</v>
-      </c>
-      <c r="G24">
-        <v>0.06193161010742188</v>
-      </c>
-      <c r="H24">
-        <v>0.6352155208587646</v>
-      </c>
-      <c r="I24">
-        <v>0.5463789701461792</v>
-      </c>
-      <c r="J24">
-        <v>0.4578336477279663</v>
-      </c>
-      <c r="K24">
-        <v>0.3235751986503601</v>
-      </c>
-      <c r="L24">
-        <v>0.1315180659294128</v>
-      </c>
-      <c r="M24">
-        <v>0.07021236419677734</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25">
+      <c r="B24" s="3">
+        <v>3.399739265441895</v>
+      </c>
+      <c r="C24" s="3">
+        <v>1.8035209178924561</v>
+      </c>
+      <c r="D24" s="3">
+        <v>1.0452935695648189</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0.71643847227096558</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0.42594873905181879</v>
+      </c>
+      <c r="G24" s="3">
+        <v>6.1914920806884773E-2</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0.65843367576599121</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0.56481480598449707</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0.47167694568634028</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0.33204859495162958</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0.13543063402175901</v>
+      </c>
+      <c r="M24" s="3">
+        <v>7.0709228515625E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B25">
-        <v>1.306623697280884</v>
+        <v>1.322335362434387</v>
       </c>
       <c r="C25">
-        <v>0.7957351207733154</v>
+        <v>0.80348998308181763</v>
       </c>
       <c r="D25">
-        <v>0.447184145450592</v>
+        <v>0.4521811306476593</v>
       </c>
       <c r="E25">
-        <v>0.2089328765869141</v>
+        <v>0.21020713448524481</v>
       </c>
       <c r="F25">
-        <v>0.02554868347942829</v>
+        <v>2.5710418820381161E-2</v>
       </c>
       <c r="G25">
-        <v>0.004435393959283829</v>
+        <v>4.4424943625926971E-3</v>
       </c>
       <c r="H25">
-        <v>0.1659074872732162</v>
+        <v>0.1840264946222305</v>
       </c>
       <c r="I25">
-        <v>0.1156914159655571</v>
+        <v>0.12658445537090299</v>
       </c>
       <c r="J25">
-        <v>0.06328912079334259</v>
+        <v>6.9599777460098267E-2</v>
       </c>
       <c r="K25">
-        <v>0.0278685949742794</v>
+        <v>2.9552733525633808E-2</v>
       </c>
       <c r="L25">
-        <v>0.01267696637660265</v>
+        <v>1.312835607677698E-2</v>
       </c>
       <c r="M25">
-        <v>0.005652892403304577</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25">
-      <c r="A26" s="1" t="s">
+        <v>5.6454776786267757E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B26">
-        <v>3.357231616973877</v>
-      </c>
-      <c r="C26">
-        <v>1.790279388427734</v>
-      </c>
-      <c r="D26">
-        <v>1.040657043457031</v>
-      </c>
-      <c r="E26">
-        <v>0.7133550047874451</v>
-      </c>
-      <c r="F26">
-        <v>0.3939589858055115</v>
-      </c>
-      <c r="G26">
-        <v>0.06193161010742188</v>
-      </c>
-      <c r="H26">
-        <v>0.5998647809028625</v>
-      </c>
-      <c r="I26">
-        <v>0.505206286907196</v>
-      </c>
-      <c r="J26">
-        <v>0.4120339751243591</v>
-      </c>
-      <c r="K26">
-        <v>0.3235751986503601</v>
-      </c>
-      <c r="L26">
-        <v>0.1315180659294128</v>
-      </c>
-      <c r="M26">
-        <v>0.07021236419677734</v>
-      </c>
-      <c r="N26">
-        <v>1.354787349700928</v>
-      </c>
-      <c r="O26">
-        <v>0.9157299995422363</v>
-      </c>
-      <c r="P26">
-        <v>0.4860937595367432</v>
-      </c>
-      <c r="Q26">
-        <v>0.1639794111251831</v>
-      </c>
-      <c r="R26">
-        <v>0.03734874725341797</v>
-      </c>
-      <c r="S26">
-        <v>0</v>
-      </c>
-      <c r="T26">
-        <v>0.2017276287078857</v>
-      </c>
-      <c r="U26">
-        <v>0.1242213249206543</v>
-      </c>
-      <c r="V26">
-        <v>0.07558679580688477</v>
-      </c>
-      <c r="W26">
-        <v>0.03885471820831299</v>
-      </c>
-      <c r="X26">
-        <v>0.008562445640563965</v>
-      </c>
-      <c r="Y26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:25">
+      <c r="B26" s="3">
+        <v>3.399739265441895</v>
+      </c>
+      <c r="C26" s="3">
+        <v>1.8035209178924561</v>
+      </c>
+      <c r="D26" s="3">
+        <v>1.0452935695648189</v>
+      </c>
+      <c r="E26" s="3">
+        <v>0.71643847227096558</v>
+      </c>
+      <c r="F26" s="3">
+        <v>0.39523285627365112</v>
+      </c>
+      <c r="G26" s="3">
+        <v>6.1914920806884773E-2</v>
+      </c>
+      <c r="H26" s="3">
+        <v>0.62427133321762085</v>
+      </c>
+      <c r="I26" s="3">
+        <v>0.52416008710861206</v>
+      </c>
+      <c r="J26" s="3">
+        <v>0.42571562528610229</v>
+      </c>
+      <c r="K26" s="3">
+        <v>0.33204859495162958</v>
+      </c>
+      <c r="L26" s="3">
+        <v>0.13543063402175901</v>
+      </c>
+      <c r="M26" s="3">
+        <v>7.0709228515625E-2</v>
+      </c>
+      <c r="N26" s="3">
+        <v>1.3656270503997801</v>
+      </c>
+      <c r="O26" s="3">
+        <v>0.9245455265045166</v>
+      </c>
+      <c r="P26" s="3">
+        <v>0.49256682395935059</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>0.1665990352630615</v>
+      </c>
+      <c r="R26" s="3">
+        <v>3.8019180297851563E-2</v>
+      </c>
+      <c r="S26" s="3">
+        <v>0</v>
+      </c>
+      <c r="T26" s="3">
+        <v>0.2127885818481445</v>
+      </c>
+      <c r="U26" s="3">
+        <v>0.12835693359375</v>
+      </c>
+      <c r="V26" s="3">
+        <v>7.7667117118835449E-2</v>
+      </c>
+      <c r="W26" s="3">
+        <v>4.0062427520751953E-2</v>
+      </c>
+      <c r="X26" s="3">
+        <v>9.5038414001464844E-3</v>
+      </c>
+      <c r="Y26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B27">
-        <v>1.564647555351257</v>
+        <v>1.583212018013</v>
       </c>
       <c r="C27">
-        <v>0.9417470693588257</v>
+        <v>0.95108115673065186</v>
       </c>
       <c r="D27">
-        <v>0.5295364856719971</v>
+        <v>0.53552097082138062</v>
       </c>
       <c r="E27">
-        <v>0.25765460729599</v>
+        <v>0.25900015234947199</v>
       </c>
       <c r="F27">
-        <v>0.04288479313254356</v>
+        <v>4.3133828788995743E-2</v>
       </c>
       <c r="G27">
-        <v>0.008964112959802151</v>
+        <v>8.9820986613631248E-3</v>
       </c>
       <c r="H27">
-        <v>0.1983606517314911</v>
+        <v>0.2114713937044144</v>
       </c>
       <c r="I27">
-        <v>0.1487933099269867</v>
+        <v>0.1552093327045441</v>
       </c>
       <c r="J27">
-        <v>0.08850594609975815</v>
+        <v>9.2416748404502869E-2</v>
       </c>
       <c r="K27">
-        <v>0.04817089065909386</v>
+        <v>5.0139766186475747E-2</v>
       </c>
       <c r="L27">
-        <v>0.02480449341237545</v>
+        <v>2.5532174855470661E-2</v>
       </c>
       <c r="M27">
-        <v>0.01156277302652597</v>
+        <v>1.151931472122669E-2</v>
       </c>
       <c r="N27">
-        <v>0.5605238676071167</v>
+        <v>0.56465339660644531</v>
       </c>
       <c r="O27">
-        <v>0.3681592345237732</v>
+        <v>0.37196233868598938</v>
       </c>
       <c r="P27">
-        <v>0.1719950437545776</v>
+        <v>0.17493551969528201</v>
       </c>
       <c r="Q27">
-        <v>0.04159406200051308</v>
+        <v>4.3223854154348373E-2</v>
       </c>
       <c r="R27">
-        <v>0.00758721586316824</v>
+        <v>8.0925766378641129E-3</v>
       </c>
       <c r="S27">
         <v>0</v>
       </c>
       <c r="T27">
-        <v>0.06388859450817108</v>
+        <v>6.9323383271694183E-2</v>
       </c>
       <c r="U27">
-        <v>0.03464308753609657</v>
+        <v>3.7246759980916977E-2</v>
       </c>
       <c r="V27">
-        <v>0.01827460899949074</v>
+        <v>1.978016272187233E-2</v>
       </c>
       <c r="W27">
-        <v>0.007499378640204668</v>
+        <v>8.3068981766700745E-3</v>
       </c>
       <c r="X27">
-        <v>0.001128934323787689</v>
+        <v>1.2907679192721839E-3</v>
       </c>
       <c r="Y27">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:25">
-      <c r="A28" s="1" t="s">
+    <row r="28" spans="1:25" s="3" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B28">
-        <v>16.93032073974609</v>
-      </c>
-      <c r="C28">
-        <v>13.43041133880615</v>
-      </c>
-      <c r="D28">
-        <v>10.27763938903809</v>
-      </c>
-      <c r="E28">
-        <v>8.96624755859375</v>
-      </c>
-      <c r="F28">
-        <v>8.388852119445801</v>
-      </c>
-      <c r="G28">
-        <v>8.084892272949219</v>
-      </c>
-      <c r="H28">
-        <v>8.422307968139648</v>
-      </c>
-      <c r="I28">
-        <v>8.258554458618164</v>
-      </c>
-      <c r="J28">
-        <v>8.10658073425293</v>
-      </c>
-      <c r="K28">
-        <v>7.966219902038574</v>
-      </c>
-      <c r="L28">
-        <v>7.838887691497803</v>
-      </c>
-      <c r="M28">
-        <v>7.724306583404541</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25">
+      <c r="B28" s="3">
+        <v>16.994462966918949</v>
+      </c>
+      <c r="C28" s="3">
+        <v>13.492313385009769</v>
+      </c>
+      <c r="D28" s="3">
+        <v>10.30897235870361</v>
+      </c>
+      <c r="E28" s="3">
+        <v>8.9735250473022461</v>
+      </c>
+      <c r="F28" s="3">
+        <v>8.391240119934082</v>
+      </c>
+      <c r="G28" s="3">
+        <v>8.0849065780639648</v>
+      </c>
+      <c r="H28" s="3">
+        <v>8.4709672927856445</v>
+      </c>
+      <c r="I28" s="3">
+        <v>8.2946195602416992</v>
+      </c>
+      <c r="J28" s="3">
+        <v>8.1319112777709961</v>
+      </c>
+      <c r="K28" s="3">
+        <v>7.9827332496643066</v>
+      </c>
+      <c r="L28" s="3">
+        <v>7.8482613563537598</v>
+      </c>
+      <c r="M28" s="3">
+        <v>7.7272152900695801</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>52</v>
       </c>
       <c r="B29">
-        <v>16.41789245605469</v>
+        <v>16.486551284790039</v>
       </c>
       <c r="C29">
-        <v>11.83307361602783</v>
+        <v>11.906759262084959</v>
       </c>
       <c r="D29">
-        <v>7.771095275878906</v>
+        <v>7.8048720359802246</v>
       </c>
       <c r="E29">
-        <v>6.171589851379395</v>
+        <v>6.1776466369628906</v>
       </c>
       <c r="F29">
-        <v>5.558428764343262</v>
+        <v>5.5596561431884766</v>
       </c>
       <c r="G29">
-        <v>5.249719619750977</v>
+        <v>5.2497158050537109</v>
       </c>
       <c r="H29">
-        <v>5.699613094329834</v>
+        <v>5.7297863960266113</v>
       </c>
       <c r="I29">
-        <v>5.587394237518311</v>
+        <v>5.6088881492614746</v>
       </c>
       <c r="J29">
-        <v>5.473801136016846</v>
+        <v>5.4892210960388184</v>
       </c>
       <c r="K29">
-        <v>5.365852832794189</v>
+        <v>5.3744511604309082</v>
       </c>
       <c r="L29">
-        <v>5.268837928771973</v>
+        <v>5.271338939666748</v>
       </c>
       <c r="M29">
-        <v>5.180771827697754</v>
+        <v>5.1774682998657227</v>
       </c>
     </row>
   </sheetData>
